--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/01_Tasarım Girdileri, Malzeme ve Ürün Ağacı/EKG-TAS-LST-02_tasarim_ve_malzeme_onay_kontrol_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/01_Tasarım Girdileri, Malzeme ve Ürün Ağacı/EKG-TAS-LST-02_tasarim_ve_malzeme_onay_kontrol_listesi.xlsx
@@ -997,7 +997,8 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-LST-02&amp;C&amp;"Arial,Regular"&amp;11Tasarım ve Malzeme Onay Kontrol Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Cam üretimine uygun kontrol maddeleri, kanıt ve gerekçeli uygulanabilirlik kararı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
